--- a/templates/site-schema-blueprint.xlsx
+++ b/templates/site-schema-blueprint.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Shopify Insertion Point</t>
+          <t>Insertion Point</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
